--- a/Result/profitability/3432.xlsx
+++ b/Result/profitability/3432.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.35</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.12375</v>
+        <v>-0.1175</v>
       </c>
       <c r="N2" t="n">
-        <v>16.4325</v>
+        <v>16.96</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.76</v>
       </c>
       <c r="M3" t="n">
-        <v>0.125</v>
+        <v>0.10375</v>
       </c>
       <c r="N3" t="n">
-        <v>17.3775</v>
+        <v>18.05125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.92</v>
       </c>
       <c r="M4" t="n">
-        <v>0.24125</v>
+        <v>0.24</v>
       </c>
       <c r="N4" t="n">
-        <v>18.46625</v>
+        <v>18.24875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.39</v>
       </c>
       <c r="M5" t="n">
-        <v>0.43625</v>
+        <v>0.44875</v>
       </c>
       <c r="N5" t="n">
-        <v>20.19</v>
+        <v>20.4275</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.77</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5674999999999999</v>
+        <v>0.5625</v>
       </c>
       <c r="N6" t="n">
-        <v>21.61625</v>
+        <v>21.745</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.85</v>
       </c>
       <c r="M7" t="n">
-        <v>0.69125</v>
+        <v>0.70375</v>
       </c>
       <c r="N7" t="n">
-        <v>22.94125</v>
+        <v>23.4725</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.78</v>
       </c>
       <c r="M8" t="n">
-        <v>0.82375</v>
+        <v>0.83</v>
       </c>
       <c r="N8" t="n">
-        <v>24.26875</v>
+        <v>24.745</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.16</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8724999999999999</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>25.3525</v>
@@ -9453,6 +9453,133 @@
       </c>
       <c r="AM71" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>3432</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>79</v>
+      </c>
+      <c r="D72" t="n">
+        <v>65</v>
+      </c>
+      <c r="E72" t="n">
+        <v>14</v>
+      </c>
+      <c r="F72" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-8.33%</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="N72" t="n">
+        <v>15.6725</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0.05000000000000002</v>
+      </c>
+      <c r="X72" t="n">
+        <v>-0.2173913043478262</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.2679324894514767</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>-0.3571428571428572</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>1.900000000000002</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0.1177929324240548</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
